--- a/Tests/module02_test_cases.xlsx
+++ b/Tests/module02_test_cases.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Module02" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Module02'!$A$1:$J$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Module02'!$A$1:$L$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,6 +36,12 @@
     <font>
       <name val="Segoe UI"/>
       <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001F4E78"/>
       <sz val="10"/>
     </font>
     <font>
@@ -109,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -117,19 +123,25 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -497,19 +509,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
     <col width="32" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="32" customWidth="1" min="10" max="10"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="9" max="9"/>
+    <col width="48" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="32" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -525,40 +539,50 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Feature ID</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Feature Name</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Objective</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Preconditions</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>TestData</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>ExpectedResult</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -577,25 +601,35 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
+          <t>M02-F01</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Single Observation Entry</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
           <t>Record Single Student Observation with Valid Ratings</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>Verify that staff can record observations for a single student across all four subjects with valid ratings (G, S, NI).</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Staff user is logged in. Batch PNV26A and student ST001 exist.</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>Student=ST001; Date=2026-07-17; IT_Rating=G; IT_Notes=Excellent coding skills; PLT_Rating=S; PLT_Notes=Active participation; English_Rating=NI; English_Notes=Needs vocabulary practice; DA_Rating=S; DA_Notes=Good design sense</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="I2" s="4" t="inlineStr">
         <is>
           <t>1. Open Scan Management;
 2. Select Batch PNV26A and Student ST001;
@@ -607,54 +641,64 @@
 8. Click Save</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="J2" s="4" t="inlineStr">
         <is>
           <t>Observation is saved successfully. A success message appears. The student's record is displayed in the list with correct ratings and notes.</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="L2" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M02-F01, Scenario: SC-01</t>
         </is>
       </c>
     </row>
     <row r="3" ht="135" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>TC-M02-002</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Module 02</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Module 02</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>M02-F01</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>Single Observation Entry</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>Record Single Student Observation with Empty Ratings</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>Verify that staff can record observations with ratings set to '-' (Not Yet Assessed) and notes empty.</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>Staff user is logged in. Batch PNV26A and student ST001 exist.</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="H3" s="8" t="inlineStr">
         <is>
           <t>Student=ST001; Date=2026-07-17; Ratings='-'; Notes=''</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="I3" s="8" t="inlineStr">
         <is>
           <t>1. Open Scan Management;
 2. Select Batch PNV26A and Student ST001;
@@ -663,17 +707,17 @@
 5. Click Save</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="J3" s="8" t="inlineStr">
         <is>
           <t>Observation is saved successfully. The ratings are stored as empty/unassessed in the database. No validation error occurs.</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J3" s="6" t="inlineStr">
+      <c r="L3" s="8" t="inlineStr">
         <is>
           <t>Related Requirement: M02-F01, Scenario: SC-01</t>
         </is>
@@ -692,25 +736,35 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>M02-F01</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Single Observation Entry</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
           <t>Record Single Student Observation with Invalid Rating</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>Verify that entering an invalid rating (other than G, S, NI, or Empty) is blocked by validation.</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Staff user is logged in. Batch PNV26A and student ST001 exist.</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Student=ST001; Date=2026-07-17; IT_Rating=A; IT_Notes=Invalid rating value</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>1. Open Scan Management;
 2. Select Batch PNV26A and Student ST001;
@@ -719,54 +773,64 @@
 5. Observe UI or click Save</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>The system prevents saving. The UI dropdown restricts selection to only G, S, NI, and '-', or displays a validation error if raw data is submitted.</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M02-F01, Scenario: SC-01, Validation Rules</t>
         </is>
       </c>
     </row>
     <row r="5" ht="135" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>TC-M02-004</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Module 02</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Module 02</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>M02-F02</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Auto Rating Suggestion</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>Auto Rating Suggestion Triggered After Typing Notes</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>Verify that the system suggests a performance rating (G, S, or NI) approximately 400ms after user stops typing notes.</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>Staff user is logged in.</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="H5" s="8" t="inlineStr">
         <is>
           <t>Subject=IT; Notes='The student solved all problems quickly and helped other classmates.'</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="I5" s="8" t="inlineStr">
         <is>
           <t>1. Open observation entry for IT;
 2. Start typing the notes: 'The student solved all problems quickly and helped other classmates.';
@@ -774,17 +838,17 @@
 4. Observe the rating selector</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="J5" s="8" t="inlineStr">
         <is>
           <t>An auto-rating suggestion (G/excellent) is automatically selected or suggested adjacent to the rating field after 400ms of inactivity.</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J5" s="6" t="inlineStr">
+      <c r="L5" s="8" t="inlineStr">
         <is>
           <t>Related Requirement: M02-F02, Scenario: SC-02</t>
         </is>
@@ -803,25 +867,35 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
+          <t>M02-F02</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Auto Rating Suggestion</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
           <t>Overwrite Auto Rating Suggestion</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>Verify that staff members can manually overwrite an auto-suggested rating.</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>Staff user is logged in. System has suggested rating 'G' after notes were typed.</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>Subject=IT; Notes='Good work but missed classes'; SuggestedRating=G; OverwrittenRating=S</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>1. Type notes that trigger a 'G' suggestion;
 2. Wait for the suggestion to appear;
@@ -829,54 +903,64 @@
 4. Click Save</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>The manually selected rating 'S' replaces the suggestion 'G'. The record is saved successfully with rating 'S'.</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="L6" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M02-F02, Scenario: SC-02</t>
         </is>
       </c>
     </row>
     <row r="7" ht="150" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>TC-M02-006</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Module 02</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Module 02</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>M02-F03</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Batch Entry – All Subjects</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>Batch Entry for All Subjects simultaneously</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>Verify that staff can record observations for multiple students across all subjects simultaneously using spreadsheet-style entry.</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>Staff user is logged in. Batch PNV26A contains multiple active students (ST001, ST002).</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>Grid of ratings and notes for ST001 and ST002.</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="I7" s="8" t="inlineStr">
         <is>
           <t>1. Open Scan Management and choose Batch Entry - All Subjects;
 2. Select Batch PNV26A and Date: 17/07/2026;
@@ -884,17 +968,17 @@
 4. Click Save All</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="J7" s="8" t="inlineStr">
         <is>
           <t>Hệ thống lưu thành công toàn bộ dữ liệu nhận xét cùng một lúc. Hiển thị thông báo lưu thành công (ví dụ: "Saved 2 students"). Dữ liệu hiển thị chính xác trong danh sách.</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J7" s="6" t="inlineStr">
+      <c r="L7" s="8" t="inlineStr">
         <is>
           <t>Related Requirement: M02-F03, Scenario: SC-03</t>
         </is>
@@ -913,25 +997,35 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
+          <t>M02-F04</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Batch Entry – By Subject</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
           <t>Batch Entry by Subject</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>Verify that teachers can enter observations for a single subject for multiple students in batch mode.</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>Staff user is logged in.</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>Subject=English; Ratings and notes for ST001, ST002, ST003.</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>1. Open Scan Management and choose Batch Entry - By Subject;
 2. Select Batch PNV26A, Date: 17/07/2026, and Subject: English;
@@ -939,54 +1033,64 @@
 4. Click Save</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>English observations are saved successfully for all selected students. Other subjects (IT, PLT, DA) for these students remain unaffected.</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="L8" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M02-F04, Scenario: SC-04</t>
         </is>
       </c>
     </row>
     <row r="9" ht="120" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>TC-M02-008</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Module 02</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Module 02</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>M02-F05</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Observation Editing</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>Edit Existing Observation Ratings and Notes</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>Verify that staff can edit the ratings and notes of an existing observation record (before the session is complete).</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>Staff user is logged in. Student ST001 has an observation on 17/07/2026.</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>Student=ST001; Date=2026-07-17; NewITRating=S; NewITNotes=Needs some improvements.</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="I9" s="8" t="inlineStr">
         <is>
           <t>1. Open Scan Management;
 2. Search for ST001 and click Edit on observation for 17/07/2026;
@@ -994,17 +1098,17 @@
 4. Click Save</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="J9" s="8" t="inlineStr">
         <is>
           <t>Observation is updated successfully. A success notification is displayed. The new rating 'S' and notes display correctly.</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J9" s="6" t="inlineStr">
+      <c r="L9" s="8" t="inlineStr">
         <is>
           <t>Related Requirement: M02-F05, Scenario: SC-05</t>
         </is>
@@ -1023,25 +1127,35 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>M02-F05</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Observation Editing</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
           <t>Observation Date Locked and Cannot Be Changed</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>Verify that the observation date of an existing record is locked and cannot be edited.</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>Staff user is logged in. Student ST001 has an observation on 17/07/2026.</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>Student=ST001; Date=2026-07-17</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>1. Open Scan Management;
 2. Select ST001 observation on 17/07/2026 and click Edit;
@@ -1049,70 +1163,80 @@
 4. Attempt to modify the date</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>The Observation Date field is disabled (read-only) and cannot be interacted with or modified.</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="K10" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="L10" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M02-F05, Scenario: SC-05, Business Rules</t>
         </is>
       </c>
     </row>
     <row r="11" ht="75" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>TC-M02-010</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Module 02</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Module 02</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>M02-F06</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Duplicate Detection &amp; Merge</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>Duplicate Observation Merged - Less Than 3 Subjects Completed</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>Verify that a duplicate student/date observation is merged into the existing record if less than 3 subjects are completed in the existing record.</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>Staff user is logged in. Student ST001 has an observation on 17/07/2026 with only IT and PLT completed.</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="H11" s="8" t="inlineStr">
         <is>
           <t>Student=ST001; Date=2026-07-17; English_Rating=S; English_Notes=Good English vocabulary; DA_Rating=S</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="I11" s="8" t="inlineStr">
         <is>
           <t>1. Submit a new observation for ST001 on 17/07/2026 with English rating 'S', notes 'Good English vocabulary', and DA rating 'S';
 2. Click Save</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="J11" s="8" t="inlineStr">
         <is>
           <t>Save is accepted. English and DA ratings are merged into the existing ST001 row. Message displays: "Added to existing session.".</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J11" s="6" t="inlineStr">
+      <c r="L11" s="8" t="inlineStr">
         <is>
           <t>Related Requirement: M02-F06, Scenario: SC-06, Rule 1</t>
         </is>
@@ -1131,95 +1255,115 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
+          <t>M02-F06</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Duplicate Detection &amp; Merge</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
           <t>Duplicate Observation Rejected - 3 or More Subjects Completed</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>Verify that a duplicate student/date observation is rejected if 3 or more subjects are already completed in the existing record.</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>Staff user is logged in. Student ST001 has an observation on 17/07/2026 with IT, PLT, and English completed.</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>Student=ST001; Date=2026-07-17; DA_Rating=G; DA_Notes=Excellent design work</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>1. Attempt to save a new observation for ST001 on 17/07/2026 containing DA rating 'G';
 2. Click Save</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>Save is rejected. Error message displays: "A feedback record for this date already exists.". New record is not saved.</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="K12" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="L12" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M02-F06, Scenario: SC-07, Rule 2</t>
         </is>
       </c>
     </row>
     <row r="13" ht="90" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>TC-M02-012</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Module 02</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Module 02</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>M02-F07</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Session Management</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>Mark Session Complete - Auto-fill N/A for Unassessed Students</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t>Verify that marking a session complete automatically fills ratings for unassessed students with N/A and closes the session.</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>Staff user is logged in. Batch PNV26A session on 17/07/2026 is complete for ST001 but ST002 has no observations.</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>Batch=PNV26A; Date=2026-07-17</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="I13" s="8" t="inlineStr">
         <is>
           <t>1. Open progress dashboard for PNV26A on 17/07/2026;
 2. Click Mark Session Complete;
 3. Check session status and ST002 record</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="J13" s="8" t="inlineStr">
         <is>
           <t>Session status becomes 'Complete'. Student ST002 is automatically filled with 'N/A' for all subjects. No unassessed students remain.</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J13" s="6" t="inlineStr">
+      <c r="L13" s="8" t="inlineStr">
         <is>
           <t>Related Requirement: M02-F07, Scenario: SC-08</t>
         </is>
@@ -1238,96 +1382,116 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
+          <t>M02-F07</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Session Management</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
           <t>Block Edits on Completed Session</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>Verify that staff cannot edit or create observations once a session is marked Complete.</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>Staff user is logged in. Batch PNV26A session on 17/07/2026 is marked Complete.</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>Batch=PNV26A; Date=2026-07-17</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>1. Open completed session for PNV26A on 17/07/2026;
 2. Try clicking Edit or Add Observation for this date;
 3. Observe UI and server response if save is sent</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>Edit/Add buttons are hidden or disabled. Server rejects any manual save attempts with error "Form may be outdated." or "Session outdated.".</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="K14" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="L14" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M02-F07, Scenario: SC-08, Business Rules</t>
         </is>
       </c>
     </row>
     <row r="15" ht="90" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>TC-M02-014</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Module 02</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Module 02</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>M02-F08</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Session Progress</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>Verify Session Progress Dashboard Indicators</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="F15" s="8" t="inlineStr">
         <is>
           <t>Verify that the progress dashboard shows accurate completion rate and lists unassessed students.</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t>Staff user is logged in. Batch PNV26A has 10 students; 4 have observations, 6 do not.</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="H15" s="8" t="inlineStr">
         <is>
           <t>Batch=PNV26A; Date=2026-07-17</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="I15" s="8" t="inlineStr">
         <is>
           <t>1. Open Scan Management;
 2. Navigate to progress details for PNV26A on 17/07/2026;
 3. Check percentage and unassessed student list</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="J15" s="8" t="inlineStr">
         <is>
           <t>Dashboard displays '40% Complete' (or '4/10 students assessed'). Status is 'Incomplete'. Names of the 6 unassessed students are listed.</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="K15" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J15" s="6" t="inlineStr">
+      <c r="L15" s="8" t="inlineStr">
         <is>
           <t>Related Requirement: M02-F08, Scenario: SC-09</t>
         </is>
@@ -1346,25 +1510,35 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
+          <t>M02-F09</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Concurrent Edit Handling</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
           <t>Three-Way Merge - Non-conflicting Concurrent Edits</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>Verify that when two staff members edit different subjects on the same observation record simultaneously, changes are merged.</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>Staff Teacher A and Teacher B are logged in. Student ST001 has IT Comment 'Good performance', English is blank.</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>ST001 observation details on 17/07/2026</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>1. Teacher A opens ST001 edit form;
 2. Teacher B opens ST001 edit form;
@@ -1372,54 +1546,64 @@
 4. Teacher A updates English Comment to 'Good English speaking' (keeping IT comment original) and clicks Save</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="J16" s="4" t="inlineStr">
         <is>
           <t>Three-way merge is successful. Saved record has IT Comment 'Excellent performance' and English Comment 'Good English speaking'. Teacher A receives warning: "Saved, but some fields were updated by another teacher."</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="K16" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="L16" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M02-F09, Scenario: SC-10, Three-Way Merge</t>
         </is>
       </c>
     </row>
     <row r="17" ht="135" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>TC-M02-016</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Module 02</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Module 02</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>M02-F09</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>Concurrent Edit Handling</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>Three-Way Merge - Conflicting Concurrent Edits</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="F17" s="8" t="inlineStr">
         <is>
           <t>Verify that when two staff members edit the same field of an observation record simultaneously, the system flags a conflict and alerts the user.</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="G17" s="8" t="inlineStr">
         <is>
           <t>Teacher A and Teacher B are logged in. Student ST001 has IT Comment 'Good performance'.</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="H17" s="8" t="inlineStr">
         <is>
           <t>ST001 observation details on 17/07/2026</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="I17" s="8" t="inlineStr">
         <is>
           <t>1. Teacher A opens ST001 edit form;
 2. Teacher B opens ST001 edit form;
@@ -1427,17 +1611,17 @@
 4. Teacher A updates IT Comment to 'Very good performance' and clicks Save after Teacher B</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="J17" s="8" t="inlineStr">
         <is>
           <t>Teacher A's save triggers a conflict warning. The system flags that the IT Comment field has a conflict. Teacher A receives warning message: "Saved, but some fields were updated by another teacher." or "Form may be outdated.", and Teacher B's value 'Excellent performance' is kept (or conflict resolution UI is shown).</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="K17" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J17" s="6" t="inlineStr">
+      <c r="L17" s="8" t="inlineStr">
         <is>
           <t>Related Requirement: M02-F09, Scenario: SC-10, Three-Way Merge</t>
         </is>
@@ -1456,79 +1640,99 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
+          <t>M02-F10</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Search, Filter &amp; Sorting</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
           <t>Search Student by Full or Partial Name</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>Verify that searching student list by full or partial name correctly filters the observation records.</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>Staff user is logged in. Student list contains 'Nguyen Van A' and 'Tran Thi B'.</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>SearchQuery1=Nguyen Van A; SearchQuery2=Thi</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="I18" s="4" t="inlineStr">
         <is>
           <t>1. Open Scan Management;
 2. Enter 'Nguyen Van A' in the Search box and observe the student list;
 3. Clear the search and enter 'Thi' in the search box; 4. Observe the student list</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>Searching 'Nguyen Van A' displays only Nguyen Van A. Searching 'Thi' displays only Tran Thi B (matching partial name 'Thi'). List updates in real-time.</t>
         </is>
       </c>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="K18" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="L18" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M02-F10, Scenario: SC-11</t>
         </is>
       </c>
     </row>
     <row r="19" ht="105" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>TC-M02-018</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>Module 02</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Module 02</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>M02-F10</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>Search, Filter &amp; Sorting</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>Filter Observations by Status</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="F19" s="8" t="inlineStr">
         <is>
           <t>Verify that staff can filter the student list by observation status (Complete / Incomplete).</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="G19" s="8" t="inlineStr">
         <is>
           <t>Staff user is logged in. Batch PNV26A contains some students with complete observations and others incomplete.</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="H19" s="8" t="inlineStr">
         <is>
           <t>StatusFilter=Incomplete</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="I19" s="8" t="inlineStr">
         <is>
           <t>1. Open Scan Management;
 2. Select Batch PNV26A;
@@ -1536,17 +1740,17 @@
 4. Observe the filtered list</t>
         </is>
       </c>
-      <c r="H19" s="6" t="inlineStr">
+      <c r="J19" s="8" t="inlineStr">
         <is>
           <t>The student list displays only students who do not have all 4 subjects completed. Students with fully completed observations are hidden.</t>
         </is>
       </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="K19" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J19" s="6" t="inlineStr">
+      <c r="L19" s="8" t="inlineStr">
         <is>
           <t>Related Requirement: M02-F10, Scenario: SC-11</t>
         </is>
@@ -1565,25 +1769,35 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
+          <t>M02-F10</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Search, Filter &amp; Sorting</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
           <t>Sort Students Alphabetically and by Completion Progress</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>Verify that the student list can be sorted alphabetically or by observation completion progress.</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>Staff user is logged in. Batch PNV26A exists.</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>SortOptions=Alphabetical, CompletionProgress</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>1. Open Scan Management;
 2. Click the Sort dropdown and select Alphabetical (A-Z);
@@ -1592,70 +1806,80 @@
 5. Verify list sorting</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>The student list rearranges correctly. Alphabetical sorting orders students by name A-Z. Completion sorting displays students with fewer completed subjects first.</t>
         </is>
       </c>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="K20" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="L20" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M02-F10, Scenario: SC-11</t>
         </is>
       </c>
     </row>
     <row r="21" ht="75" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>TC-M02-020</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Module 02</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Module 02</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>M02-F11</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Dashboard Overview</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>Verify Dashboard Stats and Observation Completion Rate</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="F21" s="8" t="inlineStr">
         <is>
           <t>Verify that the dashboard displays correct metrics for active sessions, completed sessions, and completion rate.</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="G21" s="8" t="inlineStr">
         <is>
           <t>Staff user is logged in. System has 3 active sessions (2 complete, 1 incomplete). Total 30 observation records possible, 24 completed.</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="H21" s="8" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="I21" s="8" t="inlineStr">
         <is>
           <t>1. Navigate to the Dashboard Overview page;
 2. Observe the observation-related statistics cards</t>
         </is>
       </c>
-      <c r="H21" s="6" t="inlineStr">
+      <c r="J21" s="8" t="inlineStr">
         <is>
           <t>The dashboard displays: Active Observation Sessions = 3, Completed Sessions = 2, Incomplete Sessions = 1, Observation Completion Rate = 80% (24/30). Metrics are calculated accurately.</t>
         </is>
       </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="K21" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J21" s="6" t="inlineStr">
+      <c r="L21" s="8" t="inlineStr">
         <is>
           <t>Related Requirement: M02-F11, Scenario: SC-12</t>
         </is>
@@ -1674,79 +1898,99 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
+          <t>M02-F11</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Dashboard Overview</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
           <t>Verify Dashboard Auto-refresh after Observation Data Updates</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>Verify that observation dashboard statistics update immediately when observations are completed or edited.</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>Staff user is logged in. Dashboard currently displays Completion Rate = 80%.</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>New observation saved for ST005.</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="I22" s="4" t="inlineStr">
         <is>
           <t>1. Open Scan Management and record a new observation for ST005 (completing all remaining subjects for that day);
 2. Go to Dashboard immediately;
 3. Observe the Completion Rate statistic</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>The Completion Rate percentage card on the dashboard updates immediately to a higher percentage (e.g. 83%) without requiring a browser refresh.</t>
         </is>
       </c>
-      <c r="I22" s="7" t="inlineStr">
+      <c r="K22" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="L22" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M02-F11, Scenario: SC-12</t>
         </is>
       </c>
     </row>
     <row r="23" ht="120" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>TC-M02-022</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Module 02</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Module 02</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>M02-F01</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>Single Observation Entry</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
         <is>
           <t>Record Observation Blocked with Empty Date</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="F23" s="8" t="inlineStr">
         <is>
           <t>Verify that the system blocks saving an observation if the date field is empty.</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="G23" s="8" t="inlineStr">
         <is>
           <t>Staff user is logged in.</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="H23" s="8" t="inlineStr">
         <is>
           <t>Student=ST001; Date=Empty; IT_Rating=S; IT_Notes=Good progress</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="I23" s="8" t="inlineStr">
         <is>
           <t>1. Open Scan Management;
 2. Select Student ST001;
@@ -1755,17 +1999,17 @@
 5. Click Save</t>
         </is>
       </c>
-      <c r="H23" s="6" t="inlineStr">
+      <c r="J23" s="8" t="inlineStr">
         <is>
           <t>Saving is blocked. A validation error message requires Observation Date to be selected. No record is saved.</t>
         </is>
       </c>
-      <c r="I23" s="4" t="inlineStr">
+      <c r="K23" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J23" s="6" t="inlineStr">
+      <c r="L23" s="8" t="inlineStr">
         <is>
           <t>Related Requirement: M02-F01, Scenario: SC-01, Validation Rules</t>
         </is>
@@ -1784,25 +2028,35 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
+          <t>M02-F01</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Single Observation Entry</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
           <t>Record Observation Blocked with Empty Student</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>Verify that the system blocks saving an observation if no student is selected.</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>Staff user is logged in.</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>Student=Empty; Date=2026-07-17; IT_Rating=S; IT_Notes=Good progress</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="I24" s="4" t="inlineStr">
         <is>
           <t>1. Open Scan Management;
 2. Select Date: 17/07/2026;
@@ -1811,54 +2065,64 @@
 5. Click Save</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="J24" s="4" t="inlineStr">
         <is>
           <t>Saving is blocked. A validation error message requires a student to be selected. No record is saved.</t>
         </is>
       </c>
-      <c r="I24" s="4" t="inlineStr">
+      <c r="K24" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J24" s="3" t="inlineStr">
+      <c r="L24" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M02-F01, Scenario: SC-01, Validation Rules</t>
         </is>
       </c>
     </row>
     <row r="25" ht="150" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>TC-M02-024</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Module 02</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>Module 02</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>M02-F03</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>Batch Entry – All Subjects</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
         <is>
           <t>Batch Entry All Subjects Skips Empty Student Rows</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="F25" s="8" t="inlineStr">
         <is>
           <t>Verify that batch entry for all subjects skips students with completely empty inputs and reports skipped counts.</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="G25" s="8" t="inlineStr">
         <is>
           <t>Staff user is logged in. Batch PNV26A contains active students ST001 to ST005.</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="H25" s="8" t="inlineStr">
         <is>
           <t>Batch=PNV26A; Date=2026-07-17; Inputs for ST001, ST002, ST003; ST004 and ST005 are left blank.</t>
         </is>
       </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="I25" s="8" t="inlineStr">
         <is>
           <t>1. Open Scan Management and choose Batch Entry - All Subjects;
 2. Select Batch PNV26A and Date 17/07/2026;
@@ -1867,17 +2131,17 @@
 5. Click Save All</t>
         </is>
       </c>
-      <c r="H25" s="6" t="inlineStr">
+      <c r="J25" s="8" t="inlineStr">
         <is>
           <t>Records are saved successfully for ST001, ST002, and ST003. A message displays: "Saved 3 students, Skipped 2 students". No empty records are created for ST004 and ST005.</t>
         </is>
       </c>
-      <c r="I25" s="4" t="inlineStr">
+      <c r="K25" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J25" s="6" t="inlineStr">
+      <c r="L25" s="8" t="inlineStr">
         <is>
           <t>Related Requirement: M02-F03, Scenario: SC-03, Batch Entry</t>
         </is>
@@ -1896,25 +2160,35 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
+          <t>M02-F02</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Auto Rating Suggestion</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
           <t>Auto Rating Cleared When Notes Are Erased</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>Verify that if a user types notes to trigger a rating, then erases the notes, the suggested rating is reset.</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>Staff user is logged in. System has suggested rating 'G' after notes were typed.</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="H26" s="4" t="inlineStr">
         <is>
           <t>Subject=PLT; Initial Notes='Excellent student'; Erased Notes=''</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="I26" s="4" t="inlineStr">
         <is>
           <t>1. Open observation entry for PLT;
 2. Type notes: 'Excellent student';
@@ -1923,54 +2197,64 @@
 5. Observe rating dropdown</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="J26" s="4" t="inlineStr">
         <is>
           <t>The suggested rating 'G' is cleared, and the rating dropdown resets to the default '-' (Not Yet Assessed).</t>
         </is>
       </c>
-      <c r="I26" s="7" t="inlineStr">
+      <c r="K26" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J26" s="3" t="inlineStr">
+      <c r="L26" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M02-F02, Scenario: SC-02, Auto Rating Suggestion</t>
         </is>
       </c>
     </row>
     <row r="27" ht="120" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>TC-M02-026</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>Module 02</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>Module 02</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>M02-F02</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>Auto Rating Suggestion</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
         <is>
           <t>Auto Rating Suggestion Debounced During Continuous Typing</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="F27" s="8" t="inlineStr">
         <is>
           <t>Verify that the 400ms auto-rating suggestion timer is reset (debounced) as long as typing continues.</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="G27" s="8" t="inlineStr">
         <is>
           <t>Staff user is logged in.</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
+      <c r="H27" s="8" t="inlineStr">
         <is>
           <t>Subject=IT; Notes='The student is trying very hard to solve the logic problems' typed with 200ms key pauses.</t>
         </is>
       </c>
-      <c r="G27" s="6" t="inlineStr">
+      <c r="I27" s="8" t="inlineStr">
         <is>
           <t>1. Open observation entry for IT;
 2. Type notes continuously, pausing only 200ms between words;
@@ -1978,17 +2262,17 @@
 4. Stop typing completely and wait 400ms</t>
         </is>
       </c>
-      <c r="H27" s="6" t="inlineStr">
+      <c r="J27" s="8" t="inlineStr">
         <is>
           <t>No rating suggestion is selected or triggered while the user is actively typing. The suggestion only triggers 400ms after the user stops typing completely.</t>
         </is>
       </c>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="K27" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J27" s="6" t="inlineStr">
+      <c r="L27" s="8" t="inlineStr">
         <is>
           <t>Related Requirement: M02-F02, Scenario: SC-02, Auto Rating Suggestion</t>
         </is>
@@ -2007,25 +2291,35 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
+          <t>M02-F04</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Batch Entry – By Subject</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
           <t>Batch Entry By Subject Blocks Save for Students Exceeding Merge Limit</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>Verify that Batch Entry by Subject rejects saving a student's observation if that student already has 3 or more completed subjects, while saving other students.</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>Staff user is logged in. Student ST001 has 3 completed subjects (IT, PLT, English) for date 17/07/2026. ST002 has 1 completed subject.</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="H28" s="4" t="inlineStr">
         <is>
           <t>Batch=PNV26A; Subject=English; Date=2026-07-17; ST001 English=G; ST002 English=S</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="I28" s="4" t="inlineStr">
         <is>
           <t>1. Open Batch Entry - By Subject;
 2. Select Batch PNV26A, Date: 17/07/2026, and Subject: English;
@@ -2033,71 +2327,81 @@
 4. Click Save</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
+      <c r="J28" s="4" t="inlineStr">
         <is>
           <t>ST002 English observation is saved. ST001 save is rejected with a warning/error that a record for this date already exists/exceeds merge limit. The existing ST001 record is preserved.</t>
         </is>
       </c>
-      <c r="I28" s="4" t="inlineStr">
+      <c r="K28" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J28" s="3" t="inlineStr">
+      <c r="L28" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M02-F04, Scenario: SC-04, Rule 2</t>
         </is>
       </c>
     </row>
     <row r="29" ht="90" customHeight="1">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>TC-M02-028</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>Module 02</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Module 02</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>M02-SEC</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>Access Control &amp; Security</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
         <is>
           <t>Block Student Access to Scan Management</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="F29" s="8" t="inlineStr">
         <is>
           <t>Verify that a user logged in with a Student email cannot access the Scan Management page or endpoints.</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="G29" s="8" t="inlineStr">
         <is>
           <t>User has student email account student01@student.passerellesnumeriques.org.</t>
         </is>
       </c>
-      <c r="F29" s="6" t="inlineStr">
+      <c r="H29" s="8" t="inlineStr">
         <is>
           <t>Email=student01@student.passerellesnumeriques.org</t>
         </is>
       </c>
-      <c r="G29" s="6" t="inlineStr">
+      <c r="I29" s="8" t="inlineStr">
         <is>
           <t>1. Log in to the application as student;
 2. Attempt to navigate to the Scan Management page directly via URL;
 3. Observe the system response</t>
         </is>
       </c>
-      <c r="H29" s="6" t="inlineStr">
+      <c r="J29" s="8" t="inlineStr">
         <is>
           <t>The Scan Management option is not available in the menu. Direct URL access is blocked, displaying "Access Denied" or redirecting to the Student Portal home page.</t>
         </is>
       </c>
-      <c r="I29" s="4" t="inlineStr">
+      <c r="K29" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J29" s="6" t="inlineStr">
+      <c r="L29" s="8" t="inlineStr">
         <is>
           <t>Related Requirement: General Rules, Scenario: SC-01, User Roles</t>
         </is>
@@ -2116,79 +2420,99 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
+          <t>M02-F09</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Concurrent Edit Handling</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
           <t>Concurrent Edit Saving Blocked When Session Closed</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="F30" s="4" t="inlineStr">
         <is>
           <t>Verify that if a staff member attempts to save a student observation while another staff member completes the session, the save is blocked.</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="G30" s="4" t="inlineStr">
         <is>
           <t>Staff Teacher A and Teacher B are logged in. Batch PNV26A session on 17/07/2026 is Incomplete. Student ST001 has an observation.</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
+      <c r="H30" s="4" t="inlineStr">
         <is>
           <t>Session on 17/07/2026</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr">
+      <c r="I30" s="4" t="inlineStr">
         <is>
           <t>1. Teacher A opens ST001 edit form;
 2. Teacher B goes to progress dashboard and clicks Mark Session Complete (session status becomes Complete);
 3. Teacher A edits ST001 PLT comment and clicks Save</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
+      <c r="J30" s="4" t="inlineStr">
         <is>
           <t>Teacher A's save is rejected by the server because the session has been closed. An error message "Form may be outdated." or "Session outdated." is displayed. Changes are not saved.</t>
         </is>
       </c>
-      <c r="I30" s="4" t="inlineStr">
+      <c r="K30" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J30" s="3" t="inlineStr">
+      <c r="L30" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M02-F09, Scenario: SC-10, Session Completion &amp; Concurrency</t>
         </is>
       </c>
     </row>
     <row r="31" ht="105" customHeight="1">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>TC-M02-030</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>Module 02</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>Module 02</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>M02-F07</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>Session Management</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
         <is>
           <t>Mark Session Complete with Empty Student List</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="F31" s="8" t="inlineStr">
         <is>
           <t>Verify that marking a session complete on a batch with no active students behaves gracefully and completes.</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="G31" s="8" t="inlineStr">
         <is>
           <t>Staff user is logged in. Batch PNV26B is active but has no active students.</t>
         </is>
       </c>
-      <c r="F31" s="6" t="inlineStr">
+      <c r="H31" s="8" t="inlineStr">
         <is>
           <t>Batch=PNV26B; Date=2026-07-17</t>
         </is>
       </c>
-      <c r="G31" s="6" t="inlineStr">
+      <c r="I31" s="8" t="inlineStr">
         <is>
           <t>1. Navigate to progress dashboard of PNV26B on 17/07/2026;
 2. Verify student list is empty;
@@ -2196,17 +2520,17 @@
 4. Observe the session status</t>
         </is>
       </c>
-      <c r="H31" s="6" t="inlineStr">
+      <c r="J31" s="8" t="inlineStr">
         <is>
           <t>Session status transitions to Complete successfully. Auto-filled N/A count is 0. No errors or crashes occur.</t>
         </is>
       </c>
-      <c r="I31" s="7" t="inlineStr">
+      <c r="K31" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J31" s="6" t="inlineStr">
+      <c r="L31" s="8" t="inlineStr">
         <is>
           <t>Related Requirement: M02-F07, Scenario: SC-08, Session Completion</t>
         </is>
@@ -2225,25 +2549,35 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
+          <t>M02-F07</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Session Management</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
           <t>Block Editing of Auto-filled N/A Observations</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t>Verify that once a session is completed, the auto-filled N/A observations are locked and cannot be edited.</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>Staff user is logged in. Batch PNV26A session on 17/07/2026 has been completed. Student ST002 was auto-filled with N/A.</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
+      <c r="H32" s="4" t="inlineStr">
         <is>
           <t>Student=ST002; Date=2026-07-17</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="I32" s="4" t="inlineStr">
         <is>
           <t>1. Open observation list for PNV26A on 17/07/2026;
 2. Select ST002 (showing N/A for all subjects);
@@ -2251,24 +2585,24 @@
 4. Attempt to save modifications</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
+      <c r="J32" s="4" t="inlineStr">
         <is>
           <t>Rating select boxes and comments are read-only. Edit controls are hidden or disabled. No changes can be saved.</t>
         </is>
       </c>
-      <c r="I32" s="4" t="inlineStr">
+      <c r="K32" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J32" s="3" t="inlineStr">
+      <c r="L32" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M02-F07, Scenario: SC-08, Session Completion</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J32"/>
+  <autoFilter ref="A1:L32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>